--- a/Result/profitability/2527.xlsx
+++ b/Result/profitability/2527.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>-26.76625</v>
+        <v>-28.6475</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.09</v>
       </c>
       <c r="M3" t="n">
-        <v>0.96125</v>
+        <v>0.58875</v>
       </c>
       <c r="N3" t="n">
-        <v>-27.41125</v>
+        <v>-26.86125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5700000000000001</v>
+        <v>0.7225</v>
       </c>
       <c r="N4" t="n">
-        <v>-27.0925</v>
+        <v>-29.70125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.66375</v>
+        <v>0.7425</v>
       </c>
       <c r="N5" t="n">
-        <v>-15.55625</v>
+        <v>47.8675</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6512500000000001</v>
+        <v>0.5475000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>50.34375</v>
+        <v>47.31375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>0.47</v>
+        <v>0.495</v>
       </c>
       <c r="N7" t="n">
-        <v>47.68999999999999</v>
+        <v>43.21</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.43375</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>41.93375</v>
+        <v>41.645</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>0.0925</v>
       </c>
       <c r="N9" t="n">
-        <v>41.99124999999999</v>
+        <v>41.99125</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.1175</v>
       </c>
       <c r="N10" t="n">
-        <v>42.08124999999999</v>
+        <v>42.08125</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2029,7 +2029,7 @@
         <v>0.15625</v>
       </c>
       <c r="N13" t="n">
-        <v>47.50124999999999</v>
+        <v>47.50125</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2527</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>186</v>
+      </c>
+      <c r="D75" t="n">
+        <v>139</v>
+      </c>
+      <c r="E75" t="n">
+        <v>47</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.19</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-34</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-18.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>163</v>
+      </c>
+      <c r="J75" t="n">
+        <v>130</v>
+      </c>
+      <c r="K75" t="n">
+        <v>141</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.21375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-26.495</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8434782608695652</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.309999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08399999999999996</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-7.000000000000001</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>507.39</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.052239734549979</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
